--- a/tasks/finalpool/yf-portfolio-gsheet-pdf-gcal-email/groundtruth_workspace/Portfolio_Dashboard_Reference.xlsx
+++ b/tasks/finalpool/yf-portfolio-gsheet-pdf-gcal-email/groundtruth_workspace/Portfolio_Dashboard_Reference.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Allocation_Pct</t>
+          <t>Allocation_Pc</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazon.com Inc</t>
+          <t>Amazon.com Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>185.5</v>
+        <v>218.94</v>
       </c>
       <c r="E2" t="n">
-        <v>53.96</v>
+        <v>50.19</v>
       </c>
       <c r="F2" t="n">
-        <v>10009.58</v>
+        <v>10988.6</v>
       </c>
       <c r="G2" t="n">
-        <v>19.8</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>170.25</v>
+        <v>300.88</v>
       </c>
       <c r="E3" t="n">
-        <v>58.72</v>
+        <v>57.74</v>
       </c>
       <c r="F3" t="n">
-        <v>9997.18</v>
+        <v>17372.81</v>
       </c>
       <c r="G3" t="n">
-        <v>19.7</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>155.8</v>
+        <v>239.63</v>
       </c>
       <c r="E4" t="n">
-        <v>64.18000000000001</v>
+        <v>61.66</v>
       </c>
       <c r="F4" t="n">
-        <v>10003.24</v>
+        <v>14775.59</v>
       </c>
       <c r="G4" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +550,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>210.35</v>
+        <v>293.55</v>
       </c>
       <c r="E5" t="n">
-        <v>47.54</v>
+        <v>42.12</v>
       </c>
       <c r="F5" t="n">
-        <v>10003.84</v>
+        <v>12364.33</v>
       </c>
       <c r="G5" t="n">
-        <v>19.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="6">
@@ -579,7 +579,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Exxon Mobil Corp.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>108.9</v>
+        <v>150.76</v>
       </c>
       <c r="E6" t="n">
-        <v>91.83</v>
+        <v>94.88</v>
       </c>
       <c r="F6" t="n">
-        <v>10000.29</v>
+        <v>14304.11</v>
       </c>
       <c r="G6" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
     </row>
   </sheetData>
@@ -648,13 +648,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>175</v>
+        <v>199.25</v>
       </c>
       <c r="C2" t="n">
-        <v>185.5</v>
+        <v>218.94</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>165</v>
+        <v>173.18</v>
       </c>
       <c r="C3" t="n">
-        <v>170.25</v>
+        <v>300.88</v>
       </c>
       <c r="D3" t="n">
-        <v>3.18</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -690,17 +690,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>160</v>
+        <v>162.17</v>
       </c>
       <c r="C4" t="n">
-        <v>155.8</v>
+        <v>239.63</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.63</v>
+        <v>47.76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Gain</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>195</v>
+        <v>237.41</v>
       </c>
       <c r="C5" t="n">
-        <v>210.35</v>
+        <v>293.55</v>
       </c>
       <c r="D5" t="n">
-        <v>7.87</v>
+        <v>23.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -732,17 +732,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115</v>
+        <v>105.4</v>
       </c>
       <c r="C6" t="n">
-        <v>108.9</v>
+        <v>150.76</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.3</v>
+        <v>43.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Gain</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.2</v>
+        <v>15.7</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>-4.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
     </row>
@@ -815,17 +815,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.6</v>
+        <v>24.9</v>
       </c>
       <c r="C3" t="n">
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
     </row>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="C4" t="n">
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.5</v>
+        <v>17.7</v>
       </c>
       <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>-2.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>20.5</v>
       </c>
       <c r="C6" t="n">
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
